--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c50c7e4f96017ac/報單管理/declaration-main/Import_format/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{280CDBA0-CBDE-4447-8CE6-817CD8B8AFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5563339A-FF36-4CD2-849D-0791D37AFDC5}"/>
   <bookViews>
-    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="2550" windowWidth="17280" windowHeight="9420"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -19,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$C$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -49,11 +43,23 @@
   <si>
     <t>統編</t>
   </si>
+  <si>
+    <t>86978512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西北臺慶科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FERRITE CORE 8505.90.92.00-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -237,7 +243,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -289,7 +295,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -503,26 +509,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="19.8" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.6640625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.77734375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="53.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="51.625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="13.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="84.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="53.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -531,6 +537,17 @@
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -552,11 +569,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>16130009</v>
       </c>
@@ -565,7 +582,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>54981206</v>
       </c>
@@ -574,7 +591,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>97482186</v>
       </c>
@@ -583,7 +600,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>80559251</v>
       </c>
@@ -592,7 +609,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>84566661</v>
       </c>
@@ -601,7 +618,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>80212998</v>
       </c>
@@ -610,7 +627,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>53991607</v>
       </c>
@@ -619,7 +636,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>52573942</v>
       </c>
@@ -628,7 +645,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>86436593</v>
       </c>
@@ -637,7 +654,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>54098493</v>
       </c>
@@ -646,7 +663,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>54213992</v>
       </c>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -53,6 +53,18 @@
   </si>
   <si>
     <t>FERRITE CORE 8505.90.92.00-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16255464</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快異點企業有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電子連接線 8544.42.10.00-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -509,7 +521,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -517,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="6" customWidth="1"/>
@@ -548,6 +560,17 @@
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2550" windowWidth="17280" windowHeight="9420"/>
+    <workbookView xWindow="2550" yWindow="2595" windowWidth="17280" windowHeight="9375"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -65,6 +65,19 @@
   </si>
   <si>
     <t>電子連接線 8544.42.10.00-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>83038679</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>衡星科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CABLE 8544.42.10.00-5
+CONNECTOR 8536.90.20.00-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -521,7 +534,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -529,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="6" customWidth="1"/>
@@ -571,6 +584,17 @@
       </c>
       <c r="C3" s="4" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="39" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2595" windowWidth="17280" windowHeight="9375"/>
+    <workbookView xWindow="2550" yWindow="2640" windowWidth="17280" windowHeight="9330"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -78,6 +78,90 @@
   <si>
     <t>CABLE 8544.42.10.00-5
 CONNECTOR 8536.90.20.00-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登記人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80567479</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立寰科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>純銀戒指 7113.11.00.00-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>94884497</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希恩與梅莉號商行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓03/30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>榮藝科技有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28064139</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塑料防護物 3926.90.39.00-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>庭03/30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MLCC  8532.24.00.00-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>連接器_connector 8536.90.20.00-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>97416237</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>靚川有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>76025059</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOODS PAYMENT POUCH POLYESTER  4202.32.00.20-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台灣愛光塑膠股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓03/31</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -164,13 +248,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -180,17 +261,36 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -534,7 +634,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -542,73 +642,236 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.75" style="4" customWidth="1"/>
-    <col min="4" max="4" width="53.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="2"/>
+    <col min="1" max="1" width="51.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="84.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="D1" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="D2" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="39" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="D3" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="39" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="D4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="B1:B5 B23:B1048576 C6">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="欠稅">
+  <conditionalFormatting sqref="C1:C5 C23:C1048576">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="欠稅">
       <formula>NOT(ISERROR(SEARCH("欠稅",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="非營業中">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="非營業中">
       <formula>NOT(ISERROR(SEARCH("非營業中",C1)))</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:C22">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2640" windowWidth="17280" windowHeight="9330"/>
+    <workbookView xWindow="2550" yWindow="2730" windowWidth="17280" windowHeight="9240"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -162,6 +162,56 @@
   </si>
   <si>
     <t>圓03/31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>54865001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐽昇實業有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓03/31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通知怡蓉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>積體電路IC 8542.39.00.22-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50886525</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>八均科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>積體電路IC 8542.39.00.90-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85045133</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浩旺國際有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電腦記憶體 8542.32.00.90-2
+硬盤盒零件8473.30.00.00-6
+SSD 硬盤 8523.51.00.00-0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -283,7 +333,17 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -642,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="4" customWidth="1"/>
@@ -653,7 +713,7 @@
     <col min="6" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -666,8 +726,11 @@
       <c r="D1" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -680,8 +743,11 @@
       <c r="D2" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -694,8 +760,11 @@
       <c r="D3" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="39" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -708,8 +777,11 @@
       <c r="D4" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -722,8 +794,11 @@
       <c r="D5" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
@@ -736,8 +811,11 @@
       <c r="D6" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
@@ -750,8 +828,11 @@
       <c r="D7" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
@@ -764,8 +845,11 @@
       <c r="D8" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>31</v>
       </c>
@@ -778,44 +862,71 @@
       <c r="D9" s="8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -859,18 +970,13 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B5 B23:B1048576 C6">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  <conditionalFormatting sqref="B1:B5 B23:B1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C5 C23:C1048576">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="欠稅">
-      <formula>NOT(ISERROR(SEARCH("欠稅",C1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="非營業中">
-      <formula>NOT(ISERROR(SEARCH("非營業中",C1)))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="B7:B22">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:C22">
+  <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2730" windowWidth="17280" windowHeight="9240"/>
+    <workbookView xWindow="2550" yWindow="2775" windowWidth="17280" windowHeight="9195"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -212,6 +212,33 @@
     <t>電腦記憶體 8542.32.00.90-2
 硬盤盒零件8473.30.00.00-6
 SSD 硬盤 8523.51.00.00-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29071334</t>
+  </si>
+  <si>
+    <t>隨身碟 8523.51.00.00-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓04/01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>順原國際有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70785200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPUTER PARTS 8473.30.00.00-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美商定誼科技股份有限公司台灣分公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -333,7 +360,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -341,20 +368,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -909,15 +922,29 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
+      <c r="A13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>50</v>
+      </c>
       <c r="D14" s="9"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -971,7 +998,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B5 B23:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B22">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2775" windowWidth="17280" windowHeight="9195"/>
+    <workbookView xWindow="2550" yWindow="2820" windowWidth="17280" windowHeight="9150"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -239,6 +239,20 @@
   </si>
   <si>
     <t>美商定誼科技股份有限公司台灣分公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>志航科技股份有限公司</t>
+  </si>
+  <si>
+    <t>28081828</t>
+  </si>
+  <si>
+    <t>電腦零件(散熱片)8473.30.00.00-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茹04/09</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -707,7 +721,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -892,6 +906,9 @@
       <c r="D10" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="E10" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
@@ -906,6 +923,9 @@
       <c r="D11" s="8" t="s">
         <v>32</v>
       </c>
+      <c r="E11" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
@@ -920,6 +940,9 @@
       <c r="D12" s="8" t="s">
         <v>32</v>
       </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
@@ -934,6 +957,9 @@
       <c r="D13" s="8" t="s">
         <v>47</v>
       </c>
+      <c r="E13" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
@@ -945,13 +971,26 @@
       <c r="C14" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
+      <c r="A15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="2820" windowWidth="17280" windowHeight="9150"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -253,6 +253,34 @@
   </si>
   <si>
     <t>茹04/09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22771229</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希華晶體科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客戶如果有給淨重，項次請記得鎖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓04/13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28023412</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>智晶光電股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>檢核表其他申報事項記得打，客檢核表會告知買方料號，請打在料號欄位內</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -991,44 +1019,69 @@
       <c r="D15" s="9" t="s">
         <v>55</v>
       </c>
+      <c r="E15" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -282,6 +282,40 @@
   <si>
     <t>檢核表其他申報事項記得打，客檢核表會告知買方料號，請打在料號欄位內</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42729256</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麗洸有限公司</t>
+  </si>
+  <si>
+    <t>圓04/14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INTEL CPU 8542.31.00.00-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>54673475</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨宇國際股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IC 8542.39.00.22-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>27391037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>采玥科技有限公司</t>
   </si>
 </sst>
 </file>
@@ -1058,21 +1092,49 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
+      <c r="A18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
+      <c r="A19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="D20" s="9"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="82">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -316,6 +316,46 @@
   </si>
   <si>
     <t>采玥科技有限公司</t>
+  </si>
+  <si>
+    <t>圓04/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28508041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>優亮科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMD LED 8541.41.00.90-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>53917311</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>振鈦電子有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電感 8504.50.90.00-5  IC 8542.39.00.22-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42855345</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>博宇電子股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IC 8542.39.00.22-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -436,7 +476,31 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -451,6 +515,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -783,7 +857,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -791,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="4" customWidth="1"/>
@@ -1135,30 +1209,116 @@
       <c r="C20" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="9"/>
+      <c r="D20" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
+      <c r="A21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
+      <c r="A22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B5 B23:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+  <conditionalFormatting sqref="B30:B1048576 B1:B5">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B22">
+  <conditionalFormatting sqref="B1:B21 B30:B1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B21">
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:B29">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:B29">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -264,10 +264,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>客戶如果有給淨重，項次請記得鎖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>圓04/13</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -355,6 +351,10 @@
   </si>
   <si>
     <t>IC 8542.39.00.22-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝箱單上淨重是G ，請記得反除，項次請記得鎖淨重</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -476,28 +476,11 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -857,7 +840,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1139,10 +1122,10 @@
         <v>56</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>37</v>
@@ -1150,16 +1133,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>62</v>
-      </c>
       <c r="D17" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>37</v>
@@ -1167,16 +1150,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>65</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>37</v>
@@ -1184,16 +1167,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="D19" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>37</v>
@@ -1201,16 +1184,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>37</v>
@@ -1218,16 +1201,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>75</v>
-      </c>
       <c r="D21" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>37</v>
@@ -1235,16 +1218,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="D22" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>37</v>
@@ -1252,16 +1235,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>81</v>
-      </c>
       <c r="D23" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>37</v>
@@ -1306,19 +1289,19 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B30:B1048576 B1:B5">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B21 B30:B1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="2820" windowWidth="17280" windowHeight="9150"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="86">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -355,6 +355,22 @@
   </si>
   <si>
     <t>裝箱單上淨重是G ，請記得反除，項次請記得鎖淨重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70849957</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>長華科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>監管編號:BN132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓05/04</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -840,7 +856,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -848,6 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="工作表1"/>
   <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1251,10 +1268,18 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="8"/>
+      <c r="A24" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
@@ -1310,6 +1335,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="工作表2"/>
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="89">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -366,11 +366,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>圓05/04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>監管編號:BN132</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>圓05/04</t>
+    <t>監管編號:DT094</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佳凌科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70848492</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -856,7 +868,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1275,17 +1287,31 @@
         <v>82</v>
       </c>
       <c r="C24" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>85</v>
+      <c r="E24" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="8"/>
+      <c r="A25" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="106">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -383,6 +383,66 @@
   </si>
   <si>
     <t>70848492</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80492528</t>
+  </si>
+  <si>
+    <t>普晶電子實業有限公司</t>
+  </si>
+  <si>
+    <t>IC-8542.39.00.22-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28496495</t>
+  </si>
+  <si>
+    <t>神準科技股份有限公司</t>
+  </si>
+  <si>
+    <t>空白線路板-8534.00.00.13-4 PCB-8534.00.00.90-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>83664995</t>
+  </si>
+  <si>
+    <t>捷安電子有限公司</t>
+  </si>
+  <si>
+    <t>Chip scale package-8542.39.00.90-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23176424</t>
+  </si>
+  <si>
+    <t>欣緯股份有限公司</t>
+  </si>
+  <si>
+    <t>FAN-8414.59.90.00-5(CI999999999999)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>97090111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北岩資訊有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中央處理器CPU-8542.31.00.00-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓05/06</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +564,41 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -868,7 +962,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -877,7 +971,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="4" customWidth="1"/>
@@ -1314,45 +1408,112 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="8"/>
+      <c r="A26" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="8"/>
+      <c r="A27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="8"/>
+      <c r="A28" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="8"/>
+      <c r="A29" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B30:B1048576 B1:B5">
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+  <conditionalFormatting sqref="B31:B1048576 B1:B5">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B21 B30:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  <conditionalFormatting sqref="B1:B21 B31:B1048576">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2820" windowWidth="17280" windowHeight="9150"/>
+    <workbookView xWindow="2550" yWindow="2865" windowWidth="17280" windowHeight="9105"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="134">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -443,6 +443,118 @@
   </si>
   <si>
     <t>圓05/06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丞集股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>89722331</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IC（集成電路）-8542.39.00.22-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>量子電子有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>54818319</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Integrated Circuit-8542.39.00.22-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>億冠國際科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>84457256</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDR-8473.30.00.00-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仲盈企業有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22440143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WIRE CONNECTOR-8536.69.10.00-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尚永電子有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25116719</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石英晶體諧振-8541.60.10.00-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亞歐電子有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>83175791</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>integrated circuit-8542.39.00.90-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>典暉科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29170931</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cable with connector-8544.42.10.00-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>53709215</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬碟8471.70.90.00-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾菩洛國際有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓05/07</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -564,7 +676,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill>
@@ -586,6 +698,142 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -971,7 +1219,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="4" customWidth="1"/>
@@ -1492,27 +1740,235 @@
         <v>37</v>
       </c>
     </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="8"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="8"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="5"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="8"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B31:B1048576 B1:B5">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B21 B31:B1048576">
+  <conditionalFormatting sqref="B43:B1048576 B1:B5">
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B21 B43:B1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B21">
+    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:B29">
+    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:B29">
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33">
+    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33">
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35">
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36">
     <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B29">
+  <conditionalFormatting sqref="B36">
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37">
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B29">
+  <conditionalFormatting sqref="B37">
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
+  <conditionalFormatting sqref="B38:B42">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
+  <conditionalFormatting sqref="B38:B42">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2865" windowWidth="17280" windowHeight="9105"/>
+    <workbookView xWindow="2550" yWindow="2910" windowWidth="17280" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="187">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -426,10 +426,6 @@
     <t>欣緯股份有限公司</t>
   </si>
   <si>
-    <t>FAN-8414.59.90.00-5(CI999999999999)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>97090111</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -555,6 +551,196 @@
   </si>
   <si>
     <t>圓05/07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>連接線8544.42.10.00-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28727088</t>
+  </si>
+  <si>
+    <t>振罡科技有限公司</t>
+  </si>
+  <si>
+    <t>12876863</t>
+  </si>
+  <si>
+    <t>鼎睿科技有限公司</t>
+  </si>
+  <si>
+    <t>Electro-Magnets Valve8505.90.10.00-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台灣百科精密儀器股份有限公司</t>
+  </si>
+  <si>
+    <t>53679839</t>
+  </si>
+  <si>
+    <t>集成電路8542.39.00.90-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25147092</t>
+  </si>
+  <si>
+    <t>捷明光電有限公司</t>
+  </si>
+  <si>
+    <t>27330270</t>
+  </si>
+  <si>
+    <t>濠銘科技股份有限公司</t>
+  </si>
+  <si>
+    <t>IC-8542.39.00.90-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>84469443</t>
+  </si>
+  <si>
+    <t>磐儀科技股份有限公司</t>
+  </si>
+  <si>
+    <t>連接器-8536.69.10.00-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IC-8542.39.00.90-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24560100</t>
+  </si>
+  <si>
+    <t>源壹科技股份有限公司</t>
+  </si>
+  <si>
+    <t>ELECTRONIC PARTS FOR PCB BOARD-8504.90.00.00-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>89238750</t>
+  </si>
+  <si>
+    <t>鴻呈實業股份有限公司</t>
+  </si>
+  <si>
+    <t>茹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>連接線-8536.90.20.00-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23817434</t>
+  </si>
+  <si>
+    <t>蘋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IC-8542.39.00.90-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRYSTAL-8541.60.10.00-5</t>
+  </si>
+  <si>
+    <t>23759722</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>27876927</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加工用連接線-8544.42.10.00-5</t>
+  </si>
+  <si>
+    <t>集成電路 integrated circuit-8542.39.00.90-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23989132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>線材-8544.49.10.00-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30897480</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鏡頭-9002.19.00.00-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36165005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹽光股份有限公司</t>
+  </si>
+  <si>
+    <t>86718039</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>觸摸屏-8531.90.10.00-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碩擇實業股份有限公司</t>
+  </si>
+  <si>
+    <t>23612447</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IC-8542.39.00.22-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>銓盛電子股份有限公司</t>
+  </si>
+  <si>
+    <t>宣喬科技股份有限公司</t>
+  </si>
+  <si>
+    <t>亞佳有限公司</t>
+  </si>
+  <si>
+    <t>展耀股份有限公司</t>
+  </si>
+  <si>
+    <t>銘異科技股份有限公司</t>
+  </si>
+  <si>
+    <t>利凌企業股份有限公司</t>
+  </si>
+  <si>
+    <t>FAN-8414.59.90.00-5(CI999999999999)
+SOCKET-8536.69.10.00-3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -676,28 +862,507 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+  <dxfs count="81">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1219,7 +1884,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="4" customWidth="1"/>
@@ -1706,15 +2371,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>101</v>
+      <c r="C29" s="5" t="s">
+        <v>186</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>92</v>
@@ -1725,16 +2390,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>105</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>37</v>
@@ -1742,13 +2407,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="C31" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>92</v>
@@ -1759,16 +2424,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="C32" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="D32" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>37</v>
@@ -1776,16 +2441,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="C33" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>115</v>
-      </c>
       <c r="D33" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>37</v>
@@ -1793,16 +2458,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="C34" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>37</v>
@@ -1810,16 +2475,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>122</v>
-      </c>
       <c r="D35" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>37</v>
@@ -1827,16 +2492,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="C36" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>126</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>37</v>
@@ -1844,13 +2509,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>92</v>
@@ -1861,115 +2526,415 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" s="8" t="s">
+      <c r="E38" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="8"/>
+      <c r="D39" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="8"/>
+      <c r="A40" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="8"/>
+      <c r="A41" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="8"/>
+      <c r="A42" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B43:B1048576 B1:B5">
-    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B21 B43:B1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+  <conditionalFormatting sqref="B55:B1048576 B47:B52 B1:B5">
+    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B1048576 B1:B21 B47:B52">
+    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35">
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36">
+    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36">
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38:B42">
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38:B42">
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45">
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45">
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
     <cfRule type="duplicateValues" dxfId="9" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35">
+  <conditionalFormatting sqref="B53">
     <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
+  <conditionalFormatting sqref="B54">
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B38:B42">
+  <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46:B52">
+    <cfRule type="duplicateValues" dxfId="1" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46:B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1979,8 +2944,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表2"/>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1">
@@ -2078,6 +3046,120 @@
       </c>
       <c r="B11" t="e">
         <f>MATCH(A11,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>23817434</v>
+      </c>
+      <c r="B12" t="e">
+        <f>MATCH(A12,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>23759722</v>
+      </c>
+      <c r="B13" t="e">
+        <f>MATCH(A13,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>27876927</v>
+      </c>
+      <c r="B14" t="e">
+        <f>MATCH(A14,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>34516147</v>
+      </c>
+      <c r="B15" t="e">
+        <f>MATCH(A15,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>23989132</v>
+      </c>
+      <c r="B16" t="e">
+        <f>MATCH(A16,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>23176424</v>
+      </c>
+      <c r="B17" t="e">
+        <f>MATCH(A17,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>30897480</v>
+      </c>
+      <c r="B18" t="e">
+        <f>MATCH(A18,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>36165005</v>
+      </c>
+      <c r="B19" t="e">
+        <f>MATCH(A19,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="e">
+        <f>MATCH(A20,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="e">
+        <f>MATCH(A21,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="e">
+        <f>MATCH(A22,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="e">
+        <f>MATCH(A23,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" t="e">
+        <f>MATCH(A24,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" t="e">
+        <f>MATCH(A25,工作表1!B:B,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="e">
+        <f>MATCH(A26,工作表1!B:B,0)</f>
         <v>#N/A</v>
       </c>
     </row>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="191">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -438,10 +438,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>圓05/06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>丞集股份有限公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -742,6 +738,25 @@
     <t>FAN-8414.59.90.00-5(CI999999999999)
 SOCKET-8536.69.10.00-3</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>34388240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弘力工業股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Metal Dome-8517.79.00.00-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓05/06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓</t>
   </si>
 </sst>
 </file>
@@ -862,14 +877,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="81">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="53">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -901,13 +909,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -918,6 +919,20 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -928,20 +943,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -962,20 +963,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -993,6 +980,20 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1003,230 +1004,12 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1875,7 +1658,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1884,7 +1667,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="4" customWidth="1"/>
@@ -2379,7 +2162,7 @@
         <v>99</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>92</v>
@@ -2399,7 +2182,7 @@
         <v>103</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>37</v>
@@ -2407,13 +2190,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="C31" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>92</v>
@@ -2424,16 +2207,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="C32" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="D32" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>37</v>
@@ -2441,16 +2224,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="C33" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>114</v>
-      </c>
       <c r="D33" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>37</v>
@@ -2458,16 +2241,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="C34" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>116</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>117</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>37</v>
@@ -2475,16 +2258,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>121</v>
-      </c>
       <c r="D35" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>37</v>
@@ -2492,16 +2275,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="C36" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="8" t="s">
         <v>124</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>125</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>37</v>
@@ -2509,13 +2292,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="9" t="s">
         <v>127</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>92</v>
@@ -2526,16 +2309,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>37</v>
@@ -2543,13 +2326,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>92</v>
@@ -2560,13 +2343,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>92</v>
@@ -2577,13 +2360,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="C41" s="9" t="s">
         <v>140</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>141</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>92</v>
@@ -2594,13 +2377,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>92</v>
@@ -2611,16 +2394,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>37</v>
@@ -2628,16 +2411,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C44" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>152</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>37</v>
@@ -2645,16 +2428,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>155</v>
-      </c>
       <c r="D45" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>37</v>
@@ -2662,16 +2445,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>157</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>158</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>37</v>
@@ -2679,16 +2462,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B47" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>160</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>161</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>37</v>
@@ -2696,16 +2479,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>37</v>
@@ -2713,16 +2496,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C49" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>166</v>
-      </c>
       <c r="D49" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>37</v>
@@ -2730,16 +2513,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>37</v>
@@ -2747,16 +2530,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>37</v>
@@ -2764,16 +2547,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>37</v>
@@ -2781,16 +2564,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="C53" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="D53" s="8" t="s">
         <v>175</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>176</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>37</v>
@@ -2798,143 +2581,260 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="C54" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>179</v>
-      </c>
       <c r="D54" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>37</v>
       </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="5"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="8"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="5"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="8"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="5"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="8"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="8"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="5"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="8"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="5"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="8"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="5"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="8"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="5"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="8"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="5"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="8"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="5"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="8"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="5"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="8"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="5"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="8"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="5"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="8"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="5"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B55:B1048576 B47:B52 B1:B5">
-    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B1048576 B1:B21 B47:B52">
-    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
+  <conditionalFormatting sqref="B70:B1048576 B47:B52 B1:B5">
+    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B70:B1048576 B1:B21 B47:B52">
+    <cfRule type="duplicateValues" dxfId="51" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="38" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B54 B70:B1048576">
+    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46:B52">
+    <cfRule type="duplicateValues" dxfId="13" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46:B52">
+    <cfRule type="duplicateValues" dxfId="12" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B69">
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B69">
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B69">
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B69">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B69">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="1" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2910" windowWidth="17280" windowHeight="9060"/>
+    <workbookView xWindow="2550" yWindow="2955" windowWidth="17280" windowHeight="9015"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="192">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -194,10 +194,6 @@
   </si>
   <si>
     <t>八均科技股份有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>積體電路IC 8542.39.00.90-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -757,6 +753,14 @@
   </si>
   <si>
     <t>圓</t>
+  </si>
+  <si>
+    <t>庭05/12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IC電子零件 8542.31.00.00-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -877,7 +881,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="53">
+  <dxfs count="47">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -899,6 +903,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -915,67 +926,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1658,7 +1608,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1856,10 +1806,10 @@
         <v>39</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>41</v>
+        <v>191</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>32</v>
+        <v>190</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>37</v>
@@ -1867,13 +1817,13 @@
     </row>
     <row r="12" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>32</v>
@@ -1884,16 +1834,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>37</v>
@@ -1901,16 +1851,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>50</v>
-      </c>
       <c r="D14" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>37</v>
@@ -1918,16 +1868,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>37</v>
@@ -1935,16 +1885,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>37</v>
@@ -1952,16 +1902,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="D17" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>37</v>
@@ -1969,16 +1919,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>64</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>37</v>
@@ -1986,16 +1936,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>68</v>
-      </c>
       <c r="D19" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>37</v>
@@ -2003,16 +1953,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>37</v>
@@ -2020,16 +1970,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>74</v>
-      </c>
       <c r="D21" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>37</v>
@@ -2037,16 +1987,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="D22" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>37</v>
@@ -2054,16 +2004,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="D23" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>37</v>
@@ -2071,16 +2021,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>37</v>
@@ -2088,16 +2038,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>88</v>
-      </c>
       <c r="C25" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>37</v>
@@ -2105,16 +2055,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>37</v>
@@ -2122,16 +2072,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>95</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>37</v>
@@ -2139,16 +2089,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="D28" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>37</v>
@@ -2156,16 +2106,16 @@
     </row>
     <row r="29" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>37</v>
@@ -2173,16 +2123,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>103</v>
-      </c>
       <c r="D30" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>37</v>
@@ -2190,16 +2140,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="C31" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>106</v>
-      </c>
       <c r="D31" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>37</v>
@@ -2207,16 +2157,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="C32" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="D32" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>37</v>
@@ -2224,16 +2174,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="C33" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>113</v>
-      </c>
       <c r="D33" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>37</v>
@@ -2241,16 +2191,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="C34" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>115</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>116</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>37</v>
@@ -2258,16 +2208,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>120</v>
-      </c>
       <c r="D35" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>37</v>
@@ -2275,16 +2225,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="C36" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="8" t="s">
         <v>123</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>124</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>37</v>
@@ -2292,16 +2242,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>127</v>
-      </c>
       <c r="D37" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>37</v>
@@ -2309,16 +2259,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>130</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>131</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>37</v>
@@ -2326,16 +2276,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>37</v>
@@ -2343,16 +2293,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>137</v>
-      </c>
       <c r="D40" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>37</v>
@@ -2360,16 +2310,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="C41" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>140</v>
-      </c>
       <c r="D41" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>37</v>
@@ -2377,16 +2327,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>37</v>
@@ -2394,16 +2344,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>37</v>
@@ -2411,16 +2361,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C44" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>151</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>37</v>
@@ -2428,16 +2378,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>154</v>
-      </c>
       <c r="D45" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>37</v>
@@ -2445,16 +2395,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>156</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>157</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>37</v>
@@ -2462,16 +2412,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B47" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>159</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>160</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>37</v>
@@ -2479,16 +2429,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>37</v>
@@ -2496,16 +2446,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>165</v>
-      </c>
       <c r="D49" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>37</v>
@@ -2513,16 +2463,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>37</v>
@@ -2530,16 +2480,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>37</v>
@@ -2547,16 +2497,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>37</v>
@@ -2564,16 +2514,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="C53" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="D53" s="8" t="s">
         <v>174</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>175</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>37</v>
@@ -2581,16 +2531,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="C54" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>178</v>
-      </c>
       <c r="D54" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>37</v>
@@ -2598,16 +2548,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C55" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="D55" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>37</v>
@@ -2700,141 +2650,141 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70:B1048576 B47:B52 B1:B5">
-    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70:B1048576 B1:B21 B47:B52">
-    <cfRule type="duplicateValues" dxfId="51" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="49" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="48" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="46" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="43" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="41" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="40" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="37" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="35" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="33" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="32" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="31" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="30" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="29" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="28" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="21" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B54 B70:B1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="13" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="12" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B69">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B69">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B69">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B69">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B69">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2955" windowWidth="17280" windowHeight="9015"/>
+    <workbookView xWindow="2550" yWindow="3000" windowWidth="17280" windowHeight="8970"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="195">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -634,10 +634,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>連接線-8536.90.20.00-4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>23817434</t>
   </si>
   <si>
@@ -760,6 +756,22 @@
   </si>
   <si>
     <t>IC電子零件 8542.31.00.00-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FPC軟板 8534.00.00.90-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28898028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三芳科技有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>連接線-8544.42.10.00-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1608,7 +1620,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1806,10 +1818,10 @@
         <v>39</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>37</v>
@@ -2112,7 +2124,7 @@
         <v>98</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>91</v>
@@ -2132,7 +2144,7 @@
         <v>102</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>37</v>
@@ -2401,7 +2413,7 @@
         <v>154</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>156</v>
@@ -2412,16 +2424,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B47" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>158</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>159</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>37</v>
@@ -2429,16 +2441,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>37</v>
@@ -2446,16 +2458,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>164</v>
-      </c>
       <c r="D49" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>37</v>
@@ -2463,16 +2475,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>37</v>
@@ -2480,16 +2492,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>37</v>
@@ -2497,16 +2509,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>37</v>
@@ -2514,16 +2526,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="C53" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="D53" s="8" t="s">
         <v>173</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>174</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>37</v>
@@ -2531,16 +2543,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="C54" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>177</v>
-      </c>
       <c r="D54" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>37</v>
@@ -2548,26 +2560,34 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="D55" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="5"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="8"/>
+      <c r="A56" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="3000" windowWidth="17280" windowHeight="8970"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="201">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -772,6 +772,28 @@
   </si>
   <si>
     <t>連接線-8544.42.10.00-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80318845</t>
+  </si>
+  <si>
+    <t>IC-8542.39.00.22-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松勝電子科技股份有限公司</t>
+  </si>
+  <si>
+    <t>86242864</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Digital Pressure sensor-9026.20.92.00-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玖義實業股份有限公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2588,18 +2610,43 @@
       <c r="D56" s="8" t="s">
         <v>188</v>
       </c>
+      <c r="E56" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="5"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="8"/>
+      <c r="A57" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="5"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="8"/>
+      <c r="A58" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="204">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -794,6 +794,18 @@
   </si>
   <si>
     <t>玖義實業股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16999508</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昇達科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陶瓷諧振器-8541.60.10.00-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1642,7 +1654,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2649,16 +2661,32 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="5"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="8"/>
+      <c r="A59" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
-      <c r="D60" s="8"/>
+      <c r="D60" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="3000" windowWidth="17280" windowHeight="8970"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="207">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -806,6 +806,20 @@
   </si>
   <si>
     <t>陶瓷諧振器-8541.60.10.00-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60677396</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>妍逸國際有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60677396 妍逸國際有限公司
+臺北市大安區義安里信義路４段２１０號１１樓
+(無進出口卡)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2677,10 +2691,16 @@
         <v>37</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="5"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
+    <row r="60" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>206</v>
+      </c>
       <c r="D60" s="8" t="s">
         <v>188</v>
       </c>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -819,7 +819,7 @@
   <si>
     <t>60677396 妍逸國際有限公司
 臺北市大安區義安里信義路４段２１０號１１樓
-(無進出口卡)</t>
+(未向國際貿易署登記出進口廠商資料者)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="3000" windowWidth="17280" windowHeight="8970"/>
+    <workbookView xWindow="2550" yWindow="3045" windowWidth="17280" windowHeight="8925"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="210">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -820,6 +820,18 @@
     <t>60677396 妍逸國際有限公司
 臺北市大安區義安里信義路４段２１０號１１樓
 (未向國際貿易署登記出進口廠商資料者)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22669842</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED 8541.10.90.00-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行偉企業有限公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1668,7 +1680,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2709,10 +2721,21 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="5"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="8"/>
+      <c r="A61" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="213">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -832,6 +832,19 @@
   </si>
   <si>
     <t>行偉企業有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80398360</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐘錶零件/冠蓋9114.90.00.00-6
+鐘殼零件 9112.90.00.00-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千里眼精密部件股份有限公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1680,7 +1693,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2737,11 +2750,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="5"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="8"/>
+    <row r="62" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="215">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -845,6 +845,14 @@
   </si>
   <si>
     <t>千里眼精密部件股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12739587</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千悅興業股份有限公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1693,7 +1701,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2767,10 +2775,16 @@
         <v>37</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="5"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
+    <row r="63" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>211</v>
+      </c>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="218">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -853,6 +853,18 @@
   </si>
   <si>
     <t>千悅興業股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全台晶像股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>89261652</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>監管編號BK091</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1701,7 +1713,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2785,13 +2797,29 @@
       <c r="C63" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D63" s="8"/>
+      <c r="D63" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="5"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="8"/>
+      <c r="A64" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="221">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -817,54 +817,68 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>22669842</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED 8541.10.90.00-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行偉企業有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80398360</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐘錶零件/冠蓋9114.90.00.00-6
+鐘殼零件 9112.90.00.00-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千里眼精密部件股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12739587</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千悅興業股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全台晶像股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>89261652</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>監管編號BK091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>72640878</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>60677396 妍逸國際有限公司
 臺北市大安區義安里信義路４段２１０號１１樓
 (未向國際貿易署登記出進口廠商資料者)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>22669842</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LED 8541.10.90.00-9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行偉企業有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80398360</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鐘錶零件/冠蓋9114.90.00.00-6
-鐘殼零件 9112.90.00.00-8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>千里眼精密部件股份有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12739587</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>千悅興業股份有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全台晶像股份有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>89261652</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>監管編號BK091</t>
+    <t>72640878 百通批批樂舖
+基隆市安樂區崇德路１４號１樓
+(未向國際貿易署登記出進口廠商資料者)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百通批批樂舖</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1713,7 +1727,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2744,7 +2758,7 @@
         <v>204</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>188</v>
@@ -2755,13 +2769,13 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B61" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C61" s="9" t="s">
         <v>207</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>208</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>188</v>
@@ -2772,13 +2786,13 @@
     </row>
     <row r="62" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B62" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>188</v>
@@ -2789,13 +2803,13 @@
     </row>
     <row r="63" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>188</v>
@@ -2806,13 +2820,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B64" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="C64" s="9" t="s">
         <v>216</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>217</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>188</v>
@@ -2821,31 +2835,42 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="5"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="8"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
       <c r="D66" s="8"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
       <c r="D67" s="8"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
       <c r="D68" s="8"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="3045" windowWidth="17280" windowHeight="8925"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="227">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -880,6 +880,28 @@
   <si>
     <t>百通批批樂舖</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普詮電子股份有限公司</t>
+  </si>
+  <si>
+    <t>96932086</t>
+  </si>
+  <si>
+    <t>塑膠壓條:3921.90.90.00-2
+塑膠緊固件:3926.90.39.00-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IGBT 8541.29.90.00-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天鴻科技有限公司</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1022,115 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="59">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2852,17 +2982,33 @@
         <v>37</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="5"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="8"/>
+    <row r="66" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="5"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="8"/>
+      <c r="A67" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B67" s="9">
+        <v>90479469</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
@@ -2879,141 +3025,157 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70:B1048576 B47:B52 B1:B5">
-    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70:B1048576 B1:B21 B47:B52">
-    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="44" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B54 B70:B1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="7" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="6" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B69">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B69">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B69">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B69">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B69">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B69">
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B69">
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B69">
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B69">
+    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B69">
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="3045" windowWidth="17280" windowHeight="8925"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="230">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -902,6 +902,18 @@
   </si>
   <si>
     <t>天鴻科技有限公司</t>
+  </si>
+  <si>
+    <t>53349057</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杰霆科技有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Camera Module 杰霆科技有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1022,7 +1034,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="59">
+  <dxfs count="53">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1044,6 +1056,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1060,67 +1079,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1857,7 +1815,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2995,6 +2953,9 @@
       <c r="D66" s="8" t="s">
         <v>224</v>
       </c>
+      <c r="E66" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
@@ -3009,12 +2970,26 @@
       <c r="D67" s="8" t="s">
         <v>158</v>
       </c>
+      <c r="E67" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="5"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="8"/>
+      <c r="A68" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
@@ -3025,157 +3000,157 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70:B1048576 B47:B52 B1:B5">
-    <cfRule type="duplicateValues" dxfId="58" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70:B1048576 B1:B21 B47:B52">
-    <cfRule type="duplicateValues" dxfId="57" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="55" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="54" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="53" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="52" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="51" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="50" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="49" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="48" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="46" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="43" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="41" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="40" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="37" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="35" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="33" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="32" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="31" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="30" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="29" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B54 B70:B1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="19" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="18" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B69">
-    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B69">
-    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B69">
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B69">
-    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B69">
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="3045" windowWidth="17280" windowHeight="8925"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="236">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -913,6 +913,35 @@
   </si>
   <si>
     <t>Camera Module 杰霆科技有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SWITCHES-8536.50.50.00-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05712324</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鴻琪股份有限公</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>力山科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23535300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSFET 8541.29.90.00-8
+DIODE 8541.10.90.00-9
+SWITCH 8536.50.20.00-2
+尼龍/挽繩 5607.90.90.00-9
+IC 8542.39.00.90-5
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1034,7 +1063,34 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="53">
+  <dxfs count="56">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1824,7 +1880,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="4" customWidth="1"/>
@@ -2992,165 +3048,223 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="5"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="8"/>
+      <c r="A69" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="117" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="5"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="8"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="5"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="8"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="5"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="8"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="5"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="8"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="5"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="8"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="5"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70:B1048576 B47:B52 B1:B5">
-    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70:B1048576 B1:B21 B47:B52">
-    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="50" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B54 B70:B1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="13" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="12" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B69">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B69">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B69">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B69">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B69">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B76">
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B76">
+    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B76">
+    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B76">
+    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B76">
+    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="239">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -941,6 +941,25 @@
 SWITCH 8536.50.20.00-2
 尼龍/挽繩 5607.90.90.00-9
 IC 8542.39.00.90-5
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70402132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建毅科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">鐵氟龍透明管8538.90.90.00-7
+熱縮套管8538.90.90.00-7
+光纖尾套8538.90.90.00-7
+光纖彈簧8538.90.90.00-7
+光纖連接器8536.70.00.00-2
+光纖模具鑲件7224.90.00.21-2
+光纖陶瓷插芯8538.90.90.00-7
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1063,24 +1082,179 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+  <dxfs count="73">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1871,7 +2045,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3075,11 +3249,19 @@
         <v>158</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="5"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="8"/>
+    <row r="71" spans="1:5" ht="156" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
@@ -3113,158 +3295,184 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B70:B1048576 B47:B52 B1:B5">
-    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B70:B1048576 B1:B21 B47:B52">
-    <cfRule type="duplicateValues" dxfId="54" priority="51"/>
+  <conditionalFormatting sqref="B70 B47:B52 B1:B5 B72:B1048576">
+    <cfRule type="duplicateValues" dxfId="72" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B70 B1:B21 B47:B52 B72:B1048576">
+    <cfRule type="duplicateValues" dxfId="71" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="53" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="51" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="50" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="49" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="48" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="47" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="46" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="45" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="43" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="42" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="41" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="40" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="39" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="38" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="37" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="36" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="35" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="34" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="32" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="31" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="30" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="24" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="23" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="22" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B54 B70:B1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B54 B70 B72:B1048576">
+    <cfRule type="duplicateValues" dxfId="35" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="16" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="15" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B76">
-    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B76">
-    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B76">
-    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B76">
-    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B76">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
+    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
+    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
+    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
+    <cfRule type="duplicateValues" dxfId="28" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
+    <cfRule type="duplicateValues" dxfId="27" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
     <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="3045" windowWidth="17280" windowHeight="8925"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="246">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -961,6 +961,33 @@
 光纖模具鑲件7224.90.00.21-2
 光纖陶瓷插芯8538.90.90.00-7
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>儷耀科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22101609</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大品名-FLEXIBLE PRINTED CIRCUIT BOARD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>庭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42770819</t>
+  </si>
+  <si>
+    <t>雲智匯科技服務股份有限公司</t>
+  </si>
+  <si>
+    <t>門禁考勤機 8471.90.40.00-7
+門禁控制器 8543.90.90.00-0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1082,7 +1109,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="73">
+  <dxfs count="63">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1104,6 +1131,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1131,13 +1165,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1164,97 +1191,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2045,7 +1981,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3234,6 +3170,9 @@
       <c r="D69" s="8" t="s">
         <v>158</v>
       </c>
+      <c r="E69" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="70" spans="1:5" ht="117" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
@@ -3248,6 +3187,9 @@
       <c r="D70" s="8" t="s">
         <v>158</v>
       </c>
+      <c r="E70" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="71" spans="1:5" ht="156" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
@@ -3262,18 +3204,43 @@
       <c r="D71" s="8" t="s">
         <v>158</v>
       </c>
+      <c r="E71" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="5"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="8"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="5"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="8"/>
+      <c r="A72" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
@@ -3296,183 +3263,183 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70 B47:B52 B1:B5 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="72" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70 B1:B21 B47:B52 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="71" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="70" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="69" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="68" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="67" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="66" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="65" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="64" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="63" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="62" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="61" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="60" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="59" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="58" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="57" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="56" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="55" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="54" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="53" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="52" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="51" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="50" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="49" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="48" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="47" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="45" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="44" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="43" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="42" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="41" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="40" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="39" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="38" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="37" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="36" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B54 B70 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="35" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="33" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="32" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="28" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="27" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="3045" windowWidth="17280" windowHeight="8925"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="249">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -988,6 +988,25 @@
   <si>
     <t>門禁考勤機 8471.90.40.00-7
 門禁控制器 8543.90.90.00-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23209419</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聯陽精密工具股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DRILL 8207.50.10.00-2
+End Mill 8207.70.00.00-0
+INSERT 8207.50.10.00-2
+REAMER 8208.90.90.00-6
+Special Cutter 8208.90.90.00-6
+Chamfering Cutter 8208.90.90.00-6
+Slot Mill 8207.70.00.00-0
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1109,7 +1128,71 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="70">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1981,7 +2064,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3242,11 +3325,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="5"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="8"/>
+    <row r="74" spans="1:5" ht="156" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
@@ -3263,183 +3354,183 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70 B47:B52 B1:B5 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70 B1:B21 B47:B52 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="61" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="60" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="59" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="57" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="54" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="53" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="52" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B54 B70 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="23" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="22" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="250">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -863,12 +863,6 @@
   </si>
   <si>
     <t>72640878</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>60677396 妍逸國際有限公司
-臺北市大安區義安里信義路４段２１０號１１樓
-(未向國際貿易署登記出進口廠商資料者)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1007,6 +1001,18 @@
 Chamfering Cutter 8208.90.90.00-6
 Slot Mill 8207.70.00.00-0
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60677396 妍逸國際有限公司
+臺北市大安區義安里信義路４段２１０號１１樓
+(未向國際貿易署登記出進口廠商資料者)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25147092 捷明光電有限公司
+新北市中和區秀福里自立路３５號３樓之１
+(未向國際貿易署登記出進口廠商資料者)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1128,71 +1134,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="70">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="63">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3095,7 +3037,7 @@
         <v>204</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>188</v>
@@ -3174,13 +3116,13 @@
     </row>
     <row r="65" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>217</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>188</v>
@@ -3191,16 +3133,16 @@
     </row>
     <row r="66" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B66" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="C66" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>224</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>37</v>
@@ -3208,13 +3150,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B67" s="9">
         <v>90479469</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>158</v>
@@ -3225,13 +3167,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C68" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>229</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>188</v>
@@ -3242,13 +3184,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>158</v>
@@ -3259,13 +3201,13 @@
     </row>
     <row r="70" spans="1:5" ht="117" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B70" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="C70" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>235</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>158</v>
@@ -3276,13 +3218,13 @@
     </row>
     <row r="71" spans="1:5" ht="156" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>238</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>158</v>
@@ -3293,16 +3235,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B72" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="C72" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="D72" s="8" t="s">
         <v>241</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>242</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>37</v>
@@ -3310,13 +3252,13 @@
     </row>
     <row r="73" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>245</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>158</v>
@@ -3327,23 +3269,34 @@
     </row>
     <row r="74" spans="1:5" ht="156" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>248</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="8"/>
+      <c r="E74" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
@@ -3354,183 +3307,183 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70 B47:B52 B1:B5 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="69" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70 B1:B21 B47:B52 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="68" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="67" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="66" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="65" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="64" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="63" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="62" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="60" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="59" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="58" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="57" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="56" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="55" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="54" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="53" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="51" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="48" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="47" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="43" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="42" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="41" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="40" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="39" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="38" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="37" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="34" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="33" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B54 B70 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="30" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="29" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="28" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="253">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1010,8 +1010,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>24828254</t>
+  </si>
+  <si>
+    <t>東昕精密科技股份有限公司</t>
+  </si>
+  <si>
     <t>25147092 捷明光電有限公司
 新北市中和區秀福里自立路３５號３樓之１
+(未向國際貿易署登記出進口廠商資料者)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24828254 東昕精密科技股份有限公司
+臺中市南屯區精科南路99號6樓之3
+6 F.-3, No. 99, Jingke S. Rd., Nantun Dist., Taichung City 408018, Taiwan (R.O.C.)
 (未向國際貿易署登記出進口廠商資料者)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2006,7 +2019,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3292,17 +3305,25 @@
         <v>140</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="5"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="8"/>
+    <row r="76" spans="1:5" ht="97.5" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>158</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="256">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1025,6 +1025,20 @@
     <t>24828254 東昕精密科技股份有限公司
 臺中市南屯區精科南路99號6樓之3
 6 F.-3, No. 99, Jingke S. Rd., Nantun Dist., Taichung City 408018, Taiwan (R.O.C.)
+(未向國際貿易署登記出進口廠商資料者)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漢升國際實業有限公司</t>
+  </si>
+  <si>
+    <t>82979981</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>82979981 漢升國際實業有限公司
+新竹市東區前溪里中華路一段202號1樓
+1 F., No. 202, Sec. 1, Zhonghua Rd., Qianxi Vil., East Dist., Hsinchu City 300002, Taiwan (R.O.C.)
 (未向國際貿易署登記出進口廠商資料者)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1147,7 +1161,71 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="70">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2019,7 +2097,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2028,7 +2106,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="4" customWidth="1"/>
@@ -3325,186 +3403,212 @@
         <v>158</v>
       </c>
     </row>
+    <row r="77" spans="1:5" ht="97.5" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="97.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="5"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="8"/>
+    </row>
+    <row r="79" spans="1:5" ht="97.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="5"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="8"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70 B47:B52 B1:B5 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70 B1:B21 B47:B52 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="61" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="60" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="59" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="57" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="54" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="53" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="52" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B54 B70 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="23" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="22" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B76">
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B79">
+    <cfRule type="duplicateValues" dxfId="28" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B79">
+    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B79">
+    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B79">
+    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B79">
+    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="259">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1040,6 +1040,17 @@
 新竹市東區前溪里中華路一段202號1樓
 1 F., No. 202, Sec. 1, Zhonghua Rd., Qianxi Vil., East Dist., Hsinchu City 300002, Taiwan (R.O.C.)
 (未向國際貿易署登記出進口廠商資料者)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宇量科技股份有限公司</t>
+  </si>
+  <si>
+    <t>TFT LCD MODUEL 8531.20.00.19-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2097,7 +2108,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2106,7 +2117,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.625" style="4" customWidth="1"/>
@@ -3417,18 +3428,344 @@
         <v>158</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="97.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="5"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="8"/>
-    </row>
-    <row r="79" spans="1:5" ht="97.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B78" s="9">
+        <v>70447855</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
       <c r="B79" s="9"/>
       <c r="C79" s="5"/>
       <c r="D79" s="8"/>
     </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="5"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="8"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="5"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="8"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="5"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="8"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="5"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="8"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="5"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="8"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="5"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="8"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="5"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="8"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="5"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="8"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="5"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="8"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="5"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="8"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="5"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="8"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="5"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="8"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="5"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="8"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="5"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="8"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="5"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="8"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="5"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="8"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="5"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="8"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="5"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="8"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="5"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="8"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="5"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="8"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="5"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="8"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="5"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="8"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="5"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="8"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="5"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="8"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="5"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="8"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="5"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="8"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="5"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="8"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="5"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="8"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="5"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="8"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="5"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="8"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="5"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="8"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="5"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="8"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="5"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="8"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="5"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="5"/>
+      <c r="D113" s="8"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="5"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="8"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="5"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="8"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="5"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="8"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="5"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="8"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="5"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="8"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="5"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="8"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="5"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="8"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="5"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="5"/>
+      <c r="D121" s="8"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="5"/>
+      <c r="B122" s="9"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="8"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="5"/>
+      <c r="B123" s="9"/>
+      <c r="C123" s="5"/>
+      <c r="D123" s="8"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="5"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="8"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="5"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="5"/>
+      <c r="D125" s="8"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="5"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="8"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="5"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="8"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="5"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="8"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="5"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="5"/>
+      <c r="D129" s="8"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="5"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="8"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="5"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="8"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="5"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="8"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70 B47:B52 B1:B5 B72:B1048576">
@@ -3552,19 +3889,19 @@
   <conditionalFormatting sqref="B46:B52">
     <cfRule type="duplicateValues" dxfId="29" priority="85"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B79">
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
     <cfRule type="duplicateValues" dxfId="28" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B79">
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
     <cfRule type="duplicateValues" dxfId="27" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B79">
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
     <cfRule type="duplicateValues" dxfId="26" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B79">
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
     <cfRule type="duplicateValues" dxfId="25" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B79">
+  <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
     <cfRule type="duplicateValues" dxfId="24" priority="17"/>
     <cfRule type="duplicateValues" dxfId="23" priority="18"/>
   </conditionalFormatting>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="3045" windowWidth="17280" windowHeight="8925"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="269">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -126,10 +126,6 @@
   </si>
   <si>
     <t>塑料防護物 3926.90.39.00-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>庭03/30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1052,6 +1048,49 @@
   <si>
     <t>蘋</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>揚明光學股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海關監管編號:CS526</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12800061</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>34266366</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>維樂工業股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海關監管編號:D1590</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>47255762</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台揚科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海關監管編號:CS038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>庭03/30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>庭</t>
   </si>
 </sst>
 </file>
@@ -1172,71 +1211,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="70">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="63">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2108,7 +2083,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2142,7 +2117,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2159,7 +2134,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2176,7 +2151,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="39" x14ac:dyDescent="0.25">
@@ -2193,7 +2168,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2204,13 +2179,13 @@
         <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2227,7 +2202,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2241,1224 +2216,1248 @@
         <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>24</v>
+        <v>267</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="D12" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>49</v>
-      </c>
       <c r="D14" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="D17" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>67</v>
-      </c>
       <c r="D19" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>73</v>
-      </c>
       <c r="D21" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>76</v>
-      </c>
       <c r="D22" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="D23" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>83</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>87</v>
-      </c>
       <c r="C25" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>91</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>94</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>97</v>
-      </c>
       <c r="D28" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>102</v>
-      </c>
       <c r="D30" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="C31" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>105</v>
-      </c>
       <c r="D31" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="C32" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="D32" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="C33" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>112</v>
-      </c>
       <c r="D33" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="C34" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>115</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>119</v>
-      </c>
       <c r="D35" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="C36" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>123</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>126</v>
-      </c>
       <c r="D37" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>130</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>136</v>
-      </c>
       <c r="D40" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="C41" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>139</v>
-      </c>
       <c r="D41" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C44" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>150</v>
-      </c>
       <c r="E44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>153</v>
-      </c>
       <c r="D45" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>156</v>
-      </c>
       <c r="E46" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B47" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C47" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>158</v>
-      </c>
       <c r="E47" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B49" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C49" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>163</v>
-      </c>
       <c r="D49" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="C53" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="D53" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="8" t="s">
-        <v>173</v>
-      </c>
       <c r="E53" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="C54" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>176</v>
-      </c>
       <c r="D54" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>186</v>
-      </c>
       <c r="D55" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B57" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C57" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>196</v>
-      </c>
       <c r="D57" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B58" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C58" s="9" t="s">
-        <v>199</v>
-      </c>
       <c r="D58" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C59" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B59" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>203</v>
-      </c>
       <c r="D59" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B61" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C61" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>207</v>
-      </c>
       <c r="D61" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B62" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>210</v>
-      </c>
       <c r="D62" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B64" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="C64" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C64" s="9" t="s">
-        <v>216</v>
-      </c>
       <c r="D64" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B65" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>218</v>
-      </c>
       <c r="D65" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B66" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="C66" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D66" s="8" t="s">
-        <v>223</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B67" s="9">
         <v>90479469</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C68" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>228</v>
-      </c>
       <c r="D68" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="117" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B70" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="C70" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>234</v>
-      </c>
       <c r="D70" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="156" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="B71" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>237</v>
-      </c>
       <c r="D71" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B72" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="C72" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="D72" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="D72" s="8" t="s">
-        <v>241</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B73" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>244</v>
-      </c>
       <c r="D73" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="156" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B74" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>247</v>
-      </c>
       <c r="D74" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="97.5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="97.5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B77" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="C77" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>255</v>
-      </c>
       <c r="D77" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B78" s="9">
         <v>70447855</v>
       </c>
       <c r="C78" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D78" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="D78" s="8" t="s">
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="5"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="8"/>
+      <c r="B79" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="5"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="8"/>
+      <c r="A80" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="5"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="8"/>
+      <c r="A81" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
@@ -3769,183 +3768,183 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70 B47:B52 B1:B5 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="69" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70 B1:B21 B47:B52 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="68" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="67" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="66" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="65" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="64" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="63" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="62" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="60" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="59" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="58" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="57" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="56" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="55" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="54" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="53" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="51" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="48" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="47" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="43" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="42" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="41" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="40" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="39" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="38" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="37" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="34" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="33" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B54 B70 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="30" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="29" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
-    <cfRule type="duplicateValues" dxfId="28" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
-    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
-    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
-    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
-    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Import_format/thingsToNote.xlsx
+++ b/Import_format/thingsToNote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="2550" yWindow="3045" windowWidth="17280" windowHeight="8925"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="271">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1091,6 +1091,19 @@
   </si>
   <si>
     <t>庭</t>
+  </si>
+  <si>
+    <t>創新服務股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">USB電源升壓模組-8504.90.00.00-6
+壓電陶瓷電路板-8534.00.00.90-0
+LED電路板-8534.00.00.90-0
+背光板-8529.90.90.00-8
+電路板-8534.00.00.90-0
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1211,7 +1224,71 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="70">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3374,6 +3451,9 @@
       <c r="D75" s="8" t="s">
         <v>157</v>
       </c>
+      <c r="E75" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="76" spans="1:5" ht="97.5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
@@ -3388,6 +3468,9 @@
       <c r="D76" s="8" t="s">
         <v>157</v>
       </c>
+      <c r="E76" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="77" spans="1:5" ht="97.5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
@@ -3402,6 +3485,9 @@
       <c r="D77" s="8" t="s">
         <v>157</v>
       </c>
+      <c r="E77" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
@@ -3416,6 +3502,9 @@
       <c r="D78" s="8" t="s">
         <v>257</v>
       </c>
+      <c r="E78" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
@@ -3430,6 +3519,9 @@
       <c r="D79" s="8" t="s">
         <v>268</v>
       </c>
+      <c r="E79" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
@@ -3444,8 +3536,11 @@
       <c r="D80" s="8" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>265</v>
       </c>
@@ -3458,92 +3553,103 @@
       <c r="D81" s="8" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="5"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="8"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="117" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B82" s="9">
+        <v>27472283</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
       <c r="B83" s="9"/>
       <c r="C83" s="5"/>
       <c r="D83" s="8"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
       <c r="B84" s="9"/>
       <c r="C84" s="5"/>
       <c r="D84" s="8"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
       <c r="B85" s="9"/>
       <c r="C85" s="5"/>
       <c r="D85" s="8"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
       <c r="B86" s="9"/>
       <c r="C86" s="5"/>
       <c r="D86" s="8"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
       <c r="B87" s="9"/>
       <c r="C87" s="5"/>
       <c r="D87" s="8"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
       <c r="B88" s="9"/>
       <c r="C88" s="5"/>
       <c r="D88" s="8"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
       <c r="B89" s="9"/>
       <c r="C89" s="5"/>
       <c r="D89" s="8"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
       <c r="B90" s="9"/>
       <c r="C90" s="5"/>
       <c r="D90" s="8"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
       <c r="B91" s="9"/>
       <c r="C91" s="5"/>
       <c r="D91" s="8"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" s="9"/>
       <c r="C92" s="5"/>
       <c r="D92" s="8"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="9"/>
       <c r="C93" s="5"/>
       <c r="D93" s="8"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
       <c r="B94" s="9"/>
       <c r="C94" s="5"/>
       <c r="D94" s="8"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
       <c r="B95" s="9"/>
       <c r="C95" s="5"/>
       <c r="D95" s="8"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
       <c r="B96" s="9"/>
       <c r="C96" s="5"/>
@@ -3768,183 +3874,183 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B70 B47:B52 B1:B5 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70 B1:B21 B47:B52 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="61" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B21">
-    <cfRule type="duplicateValues" dxfId="60" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="59" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B29">
-    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="57" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="54" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="53" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="52" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B54 B70 B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="23" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:B52">
-    <cfRule type="duplicateValues" dxfId="22" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B66 B68:B70 B72:B132">
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
